--- a/documents/Copy of Active Employee List_Whole Group_2026-10-14.xlsx
+++ b/documents/Copy of Active Employee List_Whole Group_2026-10-14.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SEBSA Internal Assessment Automation Web Application\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CB48EC3-7EE5-4BBF-868D-17C8ED3558B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BD19A4-0B75-45D2-8336-0C481CE4ECBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="229">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="227">
   <si>
     <t>Thiwanka Sandaruwan</t>
   </si>
@@ -383,12 +377,6 @@
     <t>Pinsara Bandara</t>
   </si>
   <si>
-    <t>Active Employee List - All Group</t>
-  </si>
-  <si>
-    <t>Emails</t>
-  </si>
-  <si>
     <t>asanka.perera@sebsaworld.com</t>
   </si>
   <si>
@@ -723,13 +711,19 @@
   </si>
   <si>
     <t>pamuda.sansika@sebsaworld.com</t>
+  </si>
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Email Address</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -740,13 +734,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -780,7 +767,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -793,71 +780,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="18">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -895,19 +824,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1022,78 +938,63 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1429,1479 +1330,1118 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:D174"/>
+  <dimension ref="A1:B172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" customWidth="1"/>
-    <col min="2" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="3" width="32.5546875" customWidth="1"/>
-    <col min="4" max="4" width="41.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.5546875" customWidth="1"/>
+    <col min="2" max="2" width="41.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:4" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
+    <row r="1" spans="1:2" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
-    </row>
-    <row r="3" spans="2:4" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B75" s="21" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="21" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A77" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A81" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B82" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B83" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A84" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B5" s="4">
+      <c r="B84" s="21" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A85" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A86" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B86" s="21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A87" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A88" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B88" s="21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A90" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B90" s="21" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A91" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B91" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B92" s="21" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B93" s="21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A94" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A95" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="4">
+      <c r="B95" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A96" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B96" s="21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A97" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A98" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" s="21" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A99" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100" s="21" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B101" s="21" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A102" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B102" s="21" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A103" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="B103" s="21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A104" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B104" s="21" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A105" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B105" s="21" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A106" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B106" s="21" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A107" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="2">
-        <v>4</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="4">
-        <v>5</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="2">
-        <v>6</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="4">
-        <v>7</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="4">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="2">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="4">
-        <v>10</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="2">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="4">
-        <v>12</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="4">
-        <v>13</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="2">
-        <v>14</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="4">
-        <v>15</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="2">
-        <v>16</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="4">
-        <v>17</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B21" s="4">
-        <v>18</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B22" s="2">
-        <v>19</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B23" s="4">
-        <v>20</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B24" s="2">
-        <v>21</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B25" s="4">
-        <v>22</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="4">
-        <v>23</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B27" s="2">
-        <v>24</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="4">
-        <v>25</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="2">
-        <v>26</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B30" s="4">
-        <v>27</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B31" s="4">
-        <v>28</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B32" s="2">
-        <v>29</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B33" s="4">
-        <v>30</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B34" s="2">
-        <v>31</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B35" s="4">
-        <v>32</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B36" s="4">
-        <v>33</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="2">
-        <v>34</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B38" s="4">
-        <v>35</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B39" s="2">
-        <v>36</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B40" s="4">
-        <v>37</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B41" s="4">
-        <v>38</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B42" s="2">
-        <v>39</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B43" s="4">
-        <v>40</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B44" s="2">
-        <v>41</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B45" s="4">
-        <v>42</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B46" s="4">
-        <v>43</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B47" s="2">
-        <v>44</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D47" s="23" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B48" s="4">
-        <v>45</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" s="23" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B49" s="2">
-        <v>46</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B50" s="4">
-        <v>47</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B51" s="4">
-        <v>48</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B52" s="2">
-        <v>49</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B53" s="4">
-        <v>50</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B54" s="2">
-        <v>51</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B55" s="4">
-        <v>52</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" s="23" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B56" s="4">
-        <v>53</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D56" s="23" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B57" s="2">
-        <v>54</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D57" s="23" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B58" s="4">
-        <v>55</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D58" s="23" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B59" s="2">
-        <v>56</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D59" s="23" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B60" s="4">
-        <v>57</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D60" s="23" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B61" s="4">
-        <v>58</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" s="23" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B62" s="2">
-        <v>59</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D62" s="23" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B63" s="4">
-        <v>60</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D63" s="23" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B64" s="2">
-        <v>61</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D64" s="23" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B65" s="4">
-        <v>62</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B66" s="4">
-        <v>63</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D66" s="23" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B67" s="2">
-        <v>64</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D67" s="23" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B68" s="4">
-        <v>65</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D68" s="23" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B69" s="2">
-        <v>66</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="23" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B70" s="4">
-        <v>67</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B71" s="4">
-        <v>68</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D71" s="23" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B72" s="2">
-        <v>69</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D72" s="23" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B73" s="4">
-        <v>70</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D73" s="23" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B74" s="2">
-        <v>71</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D74" s="23" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B75" s="4">
-        <v>72</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D75" s="23" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B76" s="4">
-        <v>73</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D76" s="23" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B77" s="2">
-        <v>74</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D77" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B78" s="4">
-        <v>75</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D78" s="23" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B79" s="2">
-        <v>76</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D79" s="23" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B80" s="4">
-        <v>77</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D80" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B81" s="4">
-        <v>78</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D81" s="23" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B82" s="2">
-        <v>79</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D82" s="23" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B83" s="4">
-        <v>80</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D83" s="23" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B84" s="2">
-        <v>81</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D84" s="23" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B85" s="4">
-        <v>82</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D85" s="23" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B86" s="4">
-        <v>83</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="23" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B87" s="2">
-        <v>84</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D87" s="23" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B88" s="4">
-        <v>85</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D88" s="23" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B89" s="2">
-        <v>86</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D89" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B90" s="4">
-        <v>87</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D90" s="23" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B91" s="4">
-        <v>88</v>
-      </c>
-      <c r="C91" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D91" s="23" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B92" s="2">
-        <v>89</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D92" s="23" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B93" s="4">
-        <v>90</v>
-      </c>
-      <c r="C93" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D93" s="23" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B94" s="2">
-        <v>91</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D94" s="23" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B95" s="4">
-        <v>92</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D95" s="23" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B96" s="4">
-        <v>93</v>
-      </c>
-      <c r="C96" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D96" s="23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B97" s="2">
-        <v>94</v>
-      </c>
-      <c r="C97" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D97" s="23" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B98" s="4">
-        <v>95</v>
-      </c>
-      <c r="C98" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D98" s="23" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="99" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B99" s="2">
-        <v>96</v>
-      </c>
-      <c r="C99" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99" s="23" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="100" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B100" s="4">
-        <v>97</v>
-      </c>
-      <c r="C100" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D100" s="23" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B101" s="4">
-        <v>98</v>
-      </c>
-      <c r="C101" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D101" s="23" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B102" s="2">
-        <v>99</v>
-      </c>
-      <c r="C102" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D102" s="23" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B103" s="4">
-        <v>100</v>
-      </c>
-      <c r="C103" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D103" s="23" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="104" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B104" s="2">
-        <v>101</v>
-      </c>
-      <c r="C104" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D104" s="23" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B105" s="4">
-        <v>102</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="D105" s="23" t="s">
+      <c r="B107" s="21" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="106" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B106" s="4">
-        <v>103</v>
-      </c>
-      <c r="C106" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D106" s="23" t="s">
+    <row r="108" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A108" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B108" s="21" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="107" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B107" s="2">
-        <v>104</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D107" s="23" t="s">
+    <row r="109" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A109" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B109" s="21" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="108" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B108" s="4">
-        <v>105</v>
-      </c>
-      <c r="C108" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D108" s="23" t="s">
+    <row r="110" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A110" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B110" s="21" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="109" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B109" s="2">
-        <v>106</v>
-      </c>
-      <c r="C109" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D109" s="23" t="s">
+    <row r="111" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A111" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B111" s="21" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="110" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B110" s="4">
-        <v>107</v>
-      </c>
-      <c r="C110" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D110" s="23" t="s">
+    <row r="112" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A112" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B112" s="21" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="111" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B111" s="4">
-        <v>108</v>
-      </c>
-      <c r="C111" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D111" s="23" t="s">
+    <row r="113" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A113" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B113" s="21" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="112" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B112" s="2">
-        <v>109</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D112" s="23" t="s">
+    <row r="114" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A114" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B114" s="21" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="113" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B113" s="4">
-        <v>110</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D113" s="23" t="s">
+    <row r="115" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A115" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B115" s="21" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="114" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B114" s="2">
-        <v>111</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D114" s="23" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B115" s="4">
-        <v>112</v>
-      </c>
-      <c r="C115" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D115" s="23" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B116" s="4">
-        <v>113</v>
-      </c>
-      <c r="C116" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D116" s="23" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B117" s="2">
-        <v>114</v>
-      </c>
-      <c r="C117" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D117" s="23" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B118" s="5"/>
-      <c r="C118" s="21"/>
-      <c r="D118" s="5"/>
-    </row>
-    <row r="119" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B119" s="5"/>
-      <c r="C119" s="21"/>
-      <c r="D119" s="5"/>
-    </row>
-    <row r="120" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B120" s="5"/>
-      <c r="C120" s="21"/>
-      <c r="D120" s="5"/>
-    </row>
-    <row r="121" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="122" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="123" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="124" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="125" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="126" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="127" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="128" spans="2:4" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="129" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="130" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="131" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="132" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="133" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="134" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="135" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="136" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="137" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="138" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="139" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="140" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="141" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="142" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="143" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="144" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="145" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="146" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="147" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="148" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="149" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="150" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="151" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="152" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="153" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="154" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="155" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="156" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="157" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="158" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="159" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="160" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="161" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="162" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="163" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="164" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="165" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="166" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="167" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="168" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="169" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="170" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="171" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="172" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="173" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
-    <row r="174" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="116" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A116" s="19"/>
+      <c r="B116" s="3"/>
+    </row>
+    <row r="117" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A117" s="19"/>
+      <c r="B117" s="3"/>
+    </row>
+    <row r="118" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A118" s="19"/>
+      <c r="B118" s="3"/>
+    </row>
+    <row r="119" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="121" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="122" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="123" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="124" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="125" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="126" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="127" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="128" spans="1:2" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="129" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="130" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="131" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="132" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="133" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="134" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="135" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="136" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="137" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="138" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="139" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="140" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="141" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="142" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="143" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="144" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="145" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="146" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="147" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="148" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="149" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="150" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="151" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="152" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="153" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="154" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="155" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="156" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="157" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="158" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="159" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="160" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="161" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="162" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="163" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="164" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="165" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="166" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="167" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="168" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="169" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="170" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="171" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="172" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:C22">
-    <sortCondition ref="C4:C22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A20">
+    <sortCondition ref="A2:A20"/>
   </sortState>
-  <mergeCells count="1">
-    <mergeCell ref="B2:D2"/>
-  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{04FC2303-C1EE-44C5-82D3-4A3B7BE42892}"/>
-    <hyperlink ref="D5" r:id="rId2" xr:uid="{5CAFEE8E-621F-49E4-A826-E7A5AFB67222}"/>
-    <hyperlink ref="D6" r:id="rId3" xr:uid="{C0C39941-E254-46B8-AB13-6C092A0922A7}"/>
-    <hyperlink ref="D7" r:id="rId4" xr:uid="{1FC53BA4-52EB-42A6-B901-56C55D77FEA8}"/>
-    <hyperlink ref="D8" r:id="rId5" xr:uid="{04E7C52B-D275-417E-9C21-A3D6290630B4}"/>
-    <hyperlink ref="D9" r:id="rId6" xr:uid="{E74107A9-80FA-4721-B576-66579A5F0D95}"/>
-    <hyperlink ref="D10" r:id="rId7" xr:uid="{D9CEDEE1-3AC8-4238-BFD2-9FAAA0D8E736}"/>
-    <hyperlink ref="D11" r:id="rId8" xr:uid="{6997FD30-B112-4B94-8073-8C8C8A06FDB9}"/>
-    <hyperlink ref="D12" r:id="rId9" xr:uid="{1C2CC50D-4453-4442-98B9-E14B07106211}"/>
-    <hyperlink ref="D13" r:id="rId10" xr:uid="{81A11631-E833-4B81-BD49-A0C5D956B6CC}"/>
-    <hyperlink ref="D14" r:id="rId11" xr:uid="{53B69849-3B09-48D1-A547-BC7B9AB8F238}"/>
-    <hyperlink ref="D15" r:id="rId12" xr:uid="{B2C86AE7-B5CF-4BCF-AA4D-2DC18955BA69}"/>
-    <hyperlink ref="D16" r:id="rId13" xr:uid="{5BFB4898-6172-41C6-8DBF-966E0FAEA2E5}"/>
-    <hyperlink ref="D17" r:id="rId14" xr:uid="{5F966691-E2F8-404E-A361-49E708D41A1A}"/>
-    <hyperlink ref="D18" r:id="rId15" xr:uid="{09855DE7-098B-4BDC-A0E5-98E1FBBE815C}"/>
-    <hyperlink ref="D19" r:id="rId16" xr:uid="{208485D2-660A-4412-B743-B86FFE69E233}"/>
-    <hyperlink ref="D20" r:id="rId17" xr:uid="{AB3AA6DB-425B-4EFC-BC0A-2EC98D497394}"/>
-    <hyperlink ref="D21" r:id="rId18" xr:uid="{23BE1404-0DD5-4837-AA2A-32E2638C424E}"/>
-    <hyperlink ref="D22" r:id="rId19" xr:uid="{991068C5-2FCF-43DC-8D19-28A07C939111}"/>
-    <hyperlink ref="D23" r:id="rId20" xr:uid="{787319BF-A5AA-4DCD-B02D-A3E89BFE4B62}"/>
-    <hyperlink ref="D24" r:id="rId21" xr:uid="{D357C5F6-779C-4140-BE8A-BED964B5BDD2}"/>
-    <hyperlink ref="D25" r:id="rId22" xr:uid="{DD9EA237-F872-4490-951A-1426DD3E74D8}"/>
-    <hyperlink ref="D26" r:id="rId23" xr:uid="{11948283-8D5A-482A-A60E-2A3D52958278}"/>
-    <hyperlink ref="D27" r:id="rId24" xr:uid="{46609460-FC20-4C2C-90D7-899BA4704138}"/>
-    <hyperlink ref="D28" r:id="rId25" xr:uid="{8A9E2C4B-41BE-47FF-8939-880BDC60062B}"/>
-    <hyperlink ref="D29" r:id="rId26" xr:uid="{6973A9C2-CE5C-4CBC-A657-A8BB69662E28}"/>
-    <hyperlink ref="D30" r:id="rId27" xr:uid="{7A81E240-DA81-4A23-B8E0-5B3CF0821A70}"/>
-    <hyperlink ref="D31" r:id="rId28" xr:uid="{535701F8-E580-437D-9AEC-246012D86EAF}"/>
-    <hyperlink ref="D32" r:id="rId29" xr:uid="{DB310DD9-2A74-43E7-AC06-42442F4D17D3}"/>
-    <hyperlink ref="D33" r:id="rId30" xr:uid="{BED3E2FE-45FC-4B1D-86CD-95FA19080C8D}"/>
-    <hyperlink ref="D34" r:id="rId31" xr:uid="{37D11A1E-9643-4EFA-96D2-2A25589FF1D8}"/>
-    <hyperlink ref="D35" r:id="rId32" xr:uid="{50AAEDC8-71B0-42E8-ABB8-30E307BA76B8}"/>
-    <hyperlink ref="D36" r:id="rId33" xr:uid="{EF3FEB88-0141-42AA-A3F2-C10FE4EEF97F}"/>
-    <hyperlink ref="D37" r:id="rId34" xr:uid="{5889CDEA-3856-42AA-94EA-B28BCE5C470B}"/>
-    <hyperlink ref="D38" r:id="rId35" xr:uid="{0F3AB75B-EBB7-4C7C-97AA-D1FDE8A409F7}"/>
-    <hyperlink ref="D41" r:id="rId36" xr:uid="{92C20F3B-3EA8-4F03-9280-94B9A099EAC4}"/>
-    <hyperlink ref="D42" r:id="rId37" xr:uid="{38D3022E-09A0-4A5E-8A26-1E1265355CDC}"/>
-    <hyperlink ref="D43" r:id="rId38" xr:uid="{70DBB606-59E9-448B-8609-E047340B235D}"/>
-    <hyperlink ref="D44" r:id="rId39" xr:uid="{4CFF8831-DE25-4962-A146-E6BF0F945A65}"/>
-    <hyperlink ref="D45" r:id="rId40" xr:uid="{285895F6-8295-439D-B8B9-CB508B9D3CAD}"/>
-    <hyperlink ref="D46" r:id="rId41" xr:uid="{285BEB61-1DCF-4CF9-8BB0-01A52C8D9DD9}"/>
-    <hyperlink ref="D47" r:id="rId42" xr:uid="{F8551C12-B366-4A66-92B8-0B5E4B8902A8}"/>
-    <hyperlink ref="D48" r:id="rId43" xr:uid="{CF47BA62-5597-4414-B2F6-76E8C1146EC5}"/>
-    <hyperlink ref="D49" r:id="rId44" xr:uid="{B10E98FA-BF90-40D2-98E5-82FBA7E975A7}"/>
-    <hyperlink ref="D50" r:id="rId45" xr:uid="{85B6D8E9-C094-4900-A06D-4C5EDD0A12D8}"/>
-    <hyperlink ref="D51" r:id="rId46" xr:uid="{B176D853-2481-4284-A447-02D3BFFAFC95}"/>
-    <hyperlink ref="D52" r:id="rId47" xr:uid="{A85B03C8-1042-4789-9A8F-41E4EB11879A}"/>
-    <hyperlink ref="D53" r:id="rId48" xr:uid="{5DBC586E-981A-4F91-9A4C-7E557E21FB46}"/>
-    <hyperlink ref="D54" r:id="rId49" xr:uid="{B0DB90DD-CE5B-43C5-A10B-4B0263B8AA36}"/>
-    <hyperlink ref="D55" r:id="rId50" xr:uid="{0E17F723-18EC-4BCC-9E78-CEB9C714B96F}"/>
-    <hyperlink ref="D56" r:id="rId51" xr:uid="{8C94F555-8D1C-4EB1-889A-D7731D69ECD0}"/>
-    <hyperlink ref="D57" r:id="rId52" xr:uid="{1F4E5DAA-1B35-49CC-904E-BA017B569455}"/>
-    <hyperlink ref="D58" r:id="rId53" xr:uid="{61C2E104-AA8F-41F5-8161-0BAA4A738FFD}"/>
-    <hyperlink ref="D59" r:id="rId54" xr:uid="{CE574AA0-D171-43F4-94EE-5B1C1DE057EA}"/>
-    <hyperlink ref="D60" r:id="rId55" xr:uid="{3A3787A7-D554-4ED6-9037-E509C24F9A55}"/>
-    <hyperlink ref="D61" r:id="rId56" xr:uid="{BC42E94F-88C6-4C94-92CB-8B0A60598229}"/>
-    <hyperlink ref="D62" r:id="rId57" xr:uid="{1F7E12EE-4D26-4EBC-85DE-27A682CE11D5}"/>
-    <hyperlink ref="D63" r:id="rId58" xr:uid="{46A9B589-D733-4503-8E57-B352B4039537}"/>
-    <hyperlink ref="D64" r:id="rId59" xr:uid="{08A5ECAF-9FDD-4685-88DF-9E13AC9C4BE5}"/>
-    <hyperlink ref="D65" r:id="rId60" xr:uid="{0BDC9B90-46AE-4915-B0DB-AC36F5FECE39}"/>
-    <hyperlink ref="D66" r:id="rId61" xr:uid="{12E4BFFA-4C3F-4DA6-9656-133F0EC6164A}"/>
-    <hyperlink ref="D67" r:id="rId62" xr:uid="{6C9BF098-5607-4600-BCF6-66AA3971F1A9}"/>
-    <hyperlink ref="D68" r:id="rId63" xr:uid="{C3727BB0-D7EC-4C2C-87B4-2B9A92E85DC5}"/>
-    <hyperlink ref="D69" r:id="rId64" xr:uid="{17EC629F-A89A-4977-B4A5-BCF3718AE6B1}"/>
-    <hyperlink ref="D70" r:id="rId65" xr:uid="{0DD41B25-0E11-41FC-A86E-D39BC4D47211}"/>
-    <hyperlink ref="D71" r:id="rId66" xr:uid="{799BFAF8-4C97-4BE7-BDB0-4E6D55F43054}"/>
-    <hyperlink ref="D72" r:id="rId67" xr:uid="{91A960E9-C425-4524-A2B1-73D46491DA1D}"/>
-    <hyperlink ref="D73" r:id="rId68" xr:uid="{0DA43513-2DEB-40AB-BB69-7877FF7BC2A3}"/>
-    <hyperlink ref="D74" r:id="rId69" xr:uid="{AAF1BE65-5981-440E-B194-AA2A407B7BB7}"/>
-    <hyperlink ref="D75" r:id="rId70" xr:uid="{E60D2D03-408B-4BED-8870-EB25BABA0F98}"/>
-    <hyperlink ref="D76" r:id="rId71" xr:uid="{FEE15936-101D-4C52-940B-1B358AB77677}"/>
-    <hyperlink ref="D77" r:id="rId72" xr:uid="{9901F07B-FA5A-41B3-A845-47BAE510AF86}"/>
-    <hyperlink ref="D78" r:id="rId73" xr:uid="{D4ED8024-2AF0-4CA9-B828-A1DB923D474B}"/>
-    <hyperlink ref="D79" r:id="rId74" xr:uid="{E173B574-E50C-44C6-840E-2A77BCDAB744}"/>
-    <hyperlink ref="D80" r:id="rId75" xr:uid="{262B5CE2-74C8-4E19-B5C2-DC439EDB8338}"/>
-    <hyperlink ref="D81" r:id="rId76" xr:uid="{2AF44B3D-BC56-4FEA-89BB-49E0225ED098}"/>
-    <hyperlink ref="D82" r:id="rId77" xr:uid="{C615D767-D47A-4657-A62F-49F9DAF50D05}"/>
-    <hyperlink ref="D83" r:id="rId78" xr:uid="{AD8983E3-6CAC-4084-8BAE-A28E24E28612}"/>
-    <hyperlink ref="D84" r:id="rId79" xr:uid="{625B454D-47A5-467A-A80B-0FA278B04D95}"/>
-    <hyperlink ref="D85" r:id="rId80" xr:uid="{C49FB600-ACD9-410D-A86A-F1955D1A4D30}"/>
-    <hyperlink ref="D86" r:id="rId81" xr:uid="{AB3CE456-9735-46BA-8936-44D529738CD4}"/>
-    <hyperlink ref="D87" r:id="rId82" xr:uid="{157C9F1C-350E-4FD0-BA18-CA6ED60AB937}"/>
-    <hyperlink ref="D88" r:id="rId83" xr:uid="{B801B4E5-3E5D-434F-9D21-E51224E5B23C}"/>
-    <hyperlink ref="D89" r:id="rId84" xr:uid="{F1DA5389-5ABA-4EA2-A5D2-0905DB284160}"/>
-    <hyperlink ref="D90" r:id="rId85" xr:uid="{AF2341B8-E139-41FF-9132-58B1F73DB048}"/>
-    <hyperlink ref="D91" r:id="rId86" xr:uid="{F6A10ED4-48A2-40CF-9B70-A19A77ECBB39}"/>
-    <hyperlink ref="D92" r:id="rId87" xr:uid="{0D3A330A-2E51-4EDF-B5C1-0B0C98766993}"/>
-    <hyperlink ref="D93" r:id="rId88" xr:uid="{EC99C25B-F570-4E39-8BD5-47648110F67B}"/>
-    <hyperlink ref="D96" r:id="rId89" xr:uid="{843362F3-C40C-48D4-A1DE-7A3D213036D6}"/>
-    <hyperlink ref="D105" r:id="rId90" xr:uid="{523D88C7-28D4-4399-B53B-EC1F55DF2C1A}"/>
-    <hyperlink ref="D106" r:id="rId91" xr:uid="{E7938682-8DDC-495A-88A0-2E63C5B826B8}"/>
-    <hyperlink ref="D107" r:id="rId92" xr:uid="{C908D229-5B2D-43BB-9BA9-90832AC744FE}"/>
-    <hyperlink ref="D108" r:id="rId93" xr:uid="{D7CC9C74-9D07-4F43-86D6-5CEEC281D1A0}"/>
-    <hyperlink ref="D109" r:id="rId94" xr:uid="{BA1EDAD2-6FEF-4AD3-AF5A-98504D708E68}"/>
-    <hyperlink ref="D110" r:id="rId95" xr:uid="{50E81E7E-B7B9-4039-8638-17B78DD042BF}"/>
-    <hyperlink ref="D111" r:id="rId96" xr:uid="{BA44487E-8645-43C7-A440-5264B38C2F27}"/>
-    <hyperlink ref="D112" r:id="rId97" xr:uid="{7273EA6E-0DA9-4BCD-ADD3-8DA65B84A235}"/>
-    <hyperlink ref="D113" r:id="rId98" xr:uid="{561D9F2D-D5BB-44B1-A44A-0F72FBEE79CB}"/>
-    <hyperlink ref="D114" r:id="rId99" xr:uid="{F8335AFA-591C-4C75-994A-2EBB6CBF20DF}"/>
-    <hyperlink ref="D115" r:id="rId100" xr:uid="{6AF37D7D-9F2C-4216-A137-F075E55C31E7}"/>
-    <hyperlink ref="D116" r:id="rId101" xr:uid="{09F490FF-831D-466D-8D83-74107E9635E1}"/>
-    <hyperlink ref="D117" r:id="rId102" xr:uid="{0BCCE79B-63B9-4396-8935-C5798CAFC287}"/>
-    <hyperlink ref="D100" r:id="rId103" xr:uid="{78F3AE8A-1B3E-4355-B565-5486F4EC2448}"/>
-    <hyperlink ref="D39" r:id="rId104" xr:uid="{B2CD4028-A0D7-4728-94E3-6FAF8D93A977}"/>
-    <hyperlink ref="D94" r:id="rId105" xr:uid="{25D447B3-E791-4C87-AF90-3C7A664BA421}"/>
-    <hyperlink ref="D95" r:id="rId106" xr:uid="{6392DCD6-CAF9-4DC8-99AB-BC2B9E776150}"/>
-    <hyperlink ref="D97" r:id="rId107" xr:uid="{C5500EB5-5F6A-4866-B02D-3117D0472868}"/>
-    <hyperlink ref="D98" r:id="rId108" xr:uid="{C4DA5F5B-1C4B-4931-8C0A-3EA280BAD24F}"/>
-    <hyperlink ref="D99" r:id="rId109" xr:uid="{9AAB2CB5-CCBE-4A22-8D53-A35A00DDA285}"/>
-    <hyperlink ref="D101" r:id="rId110" xr:uid="{18561E58-DE4D-4D1A-92FE-F62C0B738359}"/>
-    <hyperlink ref="D102" r:id="rId111" xr:uid="{B2598F79-44E0-4F77-9BCE-BE5C489B8A46}"/>
-    <hyperlink ref="D103" r:id="rId112" xr:uid="{936AA2DF-5788-4604-8EAC-C2357A9B66C5}"/>
-    <hyperlink ref="D104" r:id="rId113" xr:uid="{2E0493BB-8F2F-41A4-9BA4-33E59FAB0EDF}"/>
-    <hyperlink ref="D40" r:id="rId114" xr:uid="{F9BC551C-6629-471A-8F42-FBBFC2242EC1}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{04FC2303-C1EE-44C5-82D3-4A3B7BE42892}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{5CAFEE8E-621F-49E4-A826-E7A5AFB67222}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{C0C39941-E254-46B8-AB13-6C092A0922A7}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{1FC53BA4-52EB-42A6-B901-56C55D77FEA8}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{04E7C52B-D275-417E-9C21-A3D6290630B4}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{E74107A9-80FA-4721-B576-66579A5F0D95}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{D9CEDEE1-3AC8-4238-BFD2-9FAAA0D8E736}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{6997FD30-B112-4B94-8073-8C8C8A06FDB9}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{1C2CC50D-4453-4442-98B9-E14B07106211}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{81A11631-E833-4B81-BD49-A0C5D956B6CC}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{53B69849-3B09-48D1-A547-BC7B9AB8F238}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{B2C86AE7-B5CF-4BCF-AA4D-2DC18955BA69}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{5BFB4898-6172-41C6-8DBF-966E0FAEA2E5}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{5F966691-E2F8-404E-A361-49E708D41A1A}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{09855DE7-098B-4BDC-A0E5-98E1FBBE815C}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{208485D2-660A-4412-B743-B86FFE69E233}"/>
+    <hyperlink ref="B18" r:id="rId17" xr:uid="{AB3AA6DB-425B-4EFC-BC0A-2EC98D497394}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{23BE1404-0DD5-4837-AA2A-32E2638C424E}"/>
+    <hyperlink ref="B20" r:id="rId19" xr:uid="{991068C5-2FCF-43DC-8D19-28A07C939111}"/>
+    <hyperlink ref="B21" r:id="rId20" xr:uid="{787319BF-A5AA-4DCD-B02D-A3E89BFE4B62}"/>
+    <hyperlink ref="B22" r:id="rId21" xr:uid="{D357C5F6-779C-4140-BE8A-BED964B5BDD2}"/>
+    <hyperlink ref="B23" r:id="rId22" xr:uid="{DD9EA237-F872-4490-951A-1426DD3E74D8}"/>
+    <hyperlink ref="B24" r:id="rId23" xr:uid="{11948283-8D5A-482A-A60E-2A3D52958278}"/>
+    <hyperlink ref="B25" r:id="rId24" xr:uid="{46609460-FC20-4C2C-90D7-899BA4704138}"/>
+    <hyperlink ref="B26" r:id="rId25" xr:uid="{8A9E2C4B-41BE-47FF-8939-880BDC60062B}"/>
+    <hyperlink ref="B27" r:id="rId26" xr:uid="{6973A9C2-CE5C-4CBC-A657-A8BB69662E28}"/>
+    <hyperlink ref="B28" r:id="rId27" xr:uid="{7A81E240-DA81-4A23-B8E0-5B3CF0821A70}"/>
+    <hyperlink ref="B29" r:id="rId28" xr:uid="{535701F8-E580-437D-9AEC-246012D86EAF}"/>
+    <hyperlink ref="B30" r:id="rId29" xr:uid="{DB310DD9-2A74-43E7-AC06-42442F4D17D3}"/>
+    <hyperlink ref="B31" r:id="rId30" xr:uid="{BED3E2FE-45FC-4B1D-86CD-95FA19080C8D}"/>
+    <hyperlink ref="B32" r:id="rId31" xr:uid="{37D11A1E-9643-4EFA-96D2-2A25589FF1D8}"/>
+    <hyperlink ref="B33" r:id="rId32" xr:uid="{50AAEDC8-71B0-42E8-ABB8-30E307BA76B8}"/>
+    <hyperlink ref="B34" r:id="rId33" xr:uid="{EF3FEB88-0141-42AA-A3F2-C10FE4EEF97F}"/>
+    <hyperlink ref="B35" r:id="rId34" xr:uid="{5889CDEA-3856-42AA-94EA-B28BCE5C470B}"/>
+    <hyperlink ref="B36" r:id="rId35" xr:uid="{0F3AB75B-EBB7-4C7C-97AA-D1FDE8A409F7}"/>
+    <hyperlink ref="B39" r:id="rId36" xr:uid="{92C20F3B-3EA8-4F03-9280-94B9A099EAC4}"/>
+    <hyperlink ref="B40" r:id="rId37" xr:uid="{38D3022E-09A0-4A5E-8A26-1E1265355CDC}"/>
+    <hyperlink ref="B41" r:id="rId38" xr:uid="{70DBB606-59E9-448B-8609-E047340B235D}"/>
+    <hyperlink ref="B42" r:id="rId39" xr:uid="{4CFF8831-DE25-4962-A146-E6BF0F945A65}"/>
+    <hyperlink ref="B43" r:id="rId40" xr:uid="{285895F6-8295-439D-B8B9-CB508B9D3CAD}"/>
+    <hyperlink ref="B44" r:id="rId41" xr:uid="{285BEB61-1DCF-4CF9-8BB0-01A52C8D9DD9}"/>
+    <hyperlink ref="B45" r:id="rId42" xr:uid="{F8551C12-B366-4A66-92B8-0B5E4B8902A8}"/>
+    <hyperlink ref="B46" r:id="rId43" xr:uid="{CF47BA62-5597-4414-B2F6-76E8C1146EC5}"/>
+    <hyperlink ref="B47" r:id="rId44" xr:uid="{B10E98FA-BF90-40D2-98E5-82FBA7E975A7}"/>
+    <hyperlink ref="B48" r:id="rId45" xr:uid="{85B6D8E9-C094-4900-A06D-4C5EDD0A12D8}"/>
+    <hyperlink ref="B49" r:id="rId46" xr:uid="{B176D853-2481-4284-A447-02D3BFFAFC95}"/>
+    <hyperlink ref="B50" r:id="rId47" xr:uid="{A85B03C8-1042-4789-9A8F-41E4EB11879A}"/>
+    <hyperlink ref="B51" r:id="rId48" xr:uid="{5DBC586E-981A-4F91-9A4C-7E557E21FB46}"/>
+    <hyperlink ref="B52" r:id="rId49" xr:uid="{B0DB90DD-CE5B-43C5-A10B-4B0263B8AA36}"/>
+    <hyperlink ref="B53" r:id="rId50" xr:uid="{0E17F723-18EC-4BCC-9E78-CEB9C714B96F}"/>
+    <hyperlink ref="B54" r:id="rId51" xr:uid="{8C94F555-8D1C-4EB1-889A-D7731D69ECD0}"/>
+    <hyperlink ref="B55" r:id="rId52" xr:uid="{1F4E5DAA-1B35-49CC-904E-BA017B569455}"/>
+    <hyperlink ref="B56" r:id="rId53" xr:uid="{61C2E104-AA8F-41F5-8161-0BAA4A738FFD}"/>
+    <hyperlink ref="B57" r:id="rId54" xr:uid="{CE574AA0-D171-43F4-94EE-5B1C1DE057EA}"/>
+    <hyperlink ref="B58" r:id="rId55" xr:uid="{3A3787A7-D554-4ED6-9037-E509C24F9A55}"/>
+    <hyperlink ref="B59" r:id="rId56" xr:uid="{BC42E94F-88C6-4C94-92CB-8B0A60598229}"/>
+    <hyperlink ref="B60" r:id="rId57" xr:uid="{1F7E12EE-4D26-4EBC-85DE-27A682CE11D5}"/>
+    <hyperlink ref="B61" r:id="rId58" xr:uid="{46A9B589-D733-4503-8E57-B352B4039537}"/>
+    <hyperlink ref="B62" r:id="rId59" xr:uid="{08A5ECAF-9FDD-4685-88DF-9E13AC9C4BE5}"/>
+    <hyperlink ref="B63" r:id="rId60" xr:uid="{0BDC9B90-46AE-4915-B0DB-AC36F5FECE39}"/>
+    <hyperlink ref="B64" r:id="rId61" xr:uid="{12E4BFFA-4C3F-4DA6-9656-133F0EC6164A}"/>
+    <hyperlink ref="B65" r:id="rId62" xr:uid="{6C9BF098-5607-4600-BCF6-66AA3971F1A9}"/>
+    <hyperlink ref="B66" r:id="rId63" xr:uid="{C3727BB0-D7EC-4C2C-87B4-2B9A92E85DC5}"/>
+    <hyperlink ref="B67" r:id="rId64" xr:uid="{17EC629F-A89A-4977-B4A5-BCF3718AE6B1}"/>
+    <hyperlink ref="B68" r:id="rId65" xr:uid="{0DD41B25-0E11-41FC-A86E-D39BC4D47211}"/>
+    <hyperlink ref="B69" r:id="rId66" xr:uid="{799BFAF8-4C97-4BE7-BDB0-4E6D55F43054}"/>
+    <hyperlink ref="B70" r:id="rId67" xr:uid="{91A960E9-C425-4524-A2B1-73D46491DA1D}"/>
+    <hyperlink ref="B71" r:id="rId68" xr:uid="{0DA43513-2DEB-40AB-BB69-7877FF7BC2A3}"/>
+    <hyperlink ref="B72" r:id="rId69" xr:uid="{AAF1BE65-5981-440E-B194-AA2A407B7BB7}"/>
+    <hyperlink ref="B73" r:id="rId70" xr:uid="{E60D2D03-408B-4BED-8870-EB25BABA0F98}"/>
+    <hyperlink ref="B74" r:id="rId71" xr:uid="{FEE15936-101D-4C52-940B-1B358AB77677}"/>
+    <hyperlink ref="B75" r:id="rId72" xr:uid="{9901F07B-FA5A-41B3-A845-47BAE510AF86}"/>
+    <hyperlink ref="B76" r:id="rId73" xr:uid="{D4ED8024-2AF0-4CA9-B828-A1DB923D474B}"/>
+    <hyperlink ref="B77" r:id="rId74" xr:uid="{E173B574-E50C-44C6-840E-2A77BCDAB744}"/>
+    <hyperlink ref="B78" r:id="rId75" xr:uid="{262B5CE2-74C8-4E19-B5C2-DC439EDB8338}"/>
+    <hyperlink ref="B79" r:id="rId76" xr:uid="{2AF44B3D-BC56-4FEA-89BB-49E0225ED098}"/>
+    <hyperlink ref="B80" r:id="rId77" xr:uid="{C615D767-D47A-4657-A62F-49F9DAF50D05}"/>
+    <hyperlink ref="B81" r:id="rId78" xr:uid="{AD8983E3-6CAC-4084-8BAE-A28E24E28612}"/>
+    <hyperlink ref="B82" r:id="rId79" xr:uid="{625B454D-47A5-467A-A80B-0FA278B04D95}"/>
+    <hyperlink ref="B83" r:id="rId80" xr:uid="{C49FB600-ACD9-410D-A86A-F1955D1A4D30}"/>
+    <hyperlink ref="B84" r:id="rId81" xr:uid="{AB3CE456-9735-46BA-8936-44D529738CD4}"/>
+    <hyperlink ref="B85" r:id="rId82" xr:uid="{157C9F1C-350E-4FD0-BA18-CA6ED60AB937}"/>
+    <hyperlink ref="B86" r:id="rId83" xr:uid="{B801B4E5-3E5D-434F-9D21-E51224E5B23C}"/>
+    <hyperlink ref="B87" r:id="rId84" xr:uid="{F1DA5389-5ABA-4EA2-A5D2-0905DB284160}"/>
+    <hyperlink ref="B88" r:id="rId85" xr:uid="{AF2341B8-E139-41FF-9132-58B1F73DB048}"/>
+    <hyperlink ref="B89" r:id="rId86" xr:uid="{F6A10ED4-48A2-40CF-9B70-A19A77ECBB39}"/>
+    <hyperlink ref="B90" r:id="rId87" xr:uid="{0D3A330A-2E51-4EDF-B5C1-0B0C98766993}"/>
+    <hyperlink ref="B91" r:id="rId88" xr:uid="{EC99C25B-F570-4E39-8BD5-47648110F67B}"/>
+    <hyperlink ref="B94" r:id="rId89" xr:uid="{843362F3-C40C-48D4-A1DE-7A3D213036D6}"/>
+    <hyperlink ref="B103" r:id="rId90" xr:uid="{523D88C7-28D4-4399-B53B-EC1F55DF2C1A}"/>
+    <hyperlink ref="B104" r:id="rId91" xr:uid="{E7938682-8DDC-495A-88A0-2E63C5B826B8}"/>
+    <hyperlink ref="B105" r:id="rId92" xr:uid="{C908D229-5B2D-43BB-9BA9-90832AC744FE}"/>
+    <hyperlink ref="B106" r:id="rId93" xr:uid="{D7CC9C74-9D07-4F43-86D6-5CEEC281D1A0}"/>
+    <hyperlink ref="B107" r:id="rId94" xr:uid="{BA1EDAD2-6FEF-4AD3-AF5A-98504D708E68}"/>
+    <hyperlink ref="B108" r:id="rId95" xr:uid="{50E81E7E-B7B9-4039-8638-17B78DD042BF}"/>
+    <hyperlink ref="B109" r:id="rId96" xr:uid="{BA44487E-8645-43C7-A440-5264B38C2F27}"/>
+    <hyperlink ref="B110" r:id="rId97" xr:uid="{7273EA6E-0DA9-4BCD-ADD3-8DA65B84A235}"/>
+    <hyperlink ref="B111" r:id="rId98" xr:uid="{561D9F2D-D5BB-44B1-A44A-0F72FBEE79CB}"/>
+    <hyperlink ref="B112" r:id="rId99" xr:uid="{F8335AFA-591C-4C75-994A-2EBB6CBF20DF}"/>
+    <hyperlink ref="B113" r:id="rId100" xr:uid="{6AF37D7D-9F2C-4216-A137-F075E55C31E7}"/>
+    <hyperlink ref="B114" r:id="rId101" xr:uid="{09F490FF-831D-466D-8D83-74107E9635E1}"/>
+    <hyperlink ref="B115" r:id="rId102" xr:uid="{0BCCE79B-63B9-4396-8935-C5798CAFC287}"/>
+    <hyperlink ref="B98" r:id="rId103" xr:uid="{78F3AE8A-1B3E-4355-B565-5486F4EC2448}"/>
+    <hyperlink ref="B37" r:id="rId104" xr:uid="{B2CD4028-A0D7-4728-94E3-6FAF8D93A977}"/>
+    <hyperlink ref="B92" r:id="rId105" xr:uid="{25D447B3-E791-4C87-AF90-3C7A664BA421}"/>
+    <hyperlink ref="B93" r:id="rId106" xr:uid="{6392DCD6-CAF9-4DC8-99AB-BC2B9E776150}"/>
+    <hyperlink ref="B95" r:id="rId107" xr:uid="{C5500EB5-5F6A-4866-B02D-3117D0472868}"/>
+    <hyperlink ref="B96" r:id="rId108" xr:uid="{C4DA5F5B-1C4B-4931-8C0A-3EA280BAD24F}"/>
+    <hyperlink ref="B97" r:id="rId109" xr:uid="{9AAB2CB5-CCBE-4A22-8D53-A35A00DDA285}"/>
+    <hyperlink ref="B99" r:id="rId110" xr:uid="{18561E58-DE4D-4D1A-92FE-F62C0B738359}"/>
+    <hyperlink ref="B100" r:id="rId111" xr:uid="{B2598F79-44E0-4F77-9BCE-BE5C489B8A46}"/>
+    <hyperlink ref="B101" r:id="rId112" xr:uid="{936AA2DF-5788-4604-8EAC-C2357A9B66C5}"/>
+    <hyperlink ref="B102" r:id="rId113" xr:uid="{2E0493BB-8F2F-41A4-9BA4-33E59FAB0EDF}"/>
+    <hyperlink ref="B38" r:id="rId114" xr:uid="{F9BC551C-6629-471A-8F42-FBBFC2242EC1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
